--- a/test/input/表面结果通知台账测试/生成器台账.xlsx
+++ b/test/input/表面结果通知台账测试/生成器台账.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\code\report-generator\test\input\表面结果通知台账测试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B306B4-F2B9-42DE-9071-4F300CDA6DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB8AB86-325E-4C00-9A79-2B8351BD7A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13440" yWindow="4950" windowWidth="24690" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="79">
   <si>
     <t>委托日期</t>
   </si>
@@ -126,9 +126,6 @@
     <t>/</t>
   </si>
   <si>
-    <t>1道</t>
-  </si>
-  <si>
     <t>焊后</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
   </si>
   <si>
     <t>20#</t>
-  </si>
-  <si>
-    <t>0.4m</t>
   </si>
   <si>
     <t>5127-LN-91028-600-C1C</t>
@@ -264,19 +258,11 @@
     <t>W39</t>
   </si>
   <si>
-    <t>0.4m</t>
+    <t>2024.08.7</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>0.4456m</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.54m</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>2024.08.7</t>
+    <t>1点</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -1087,7 +1073,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="61" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>23</v>
@@ -1130,37 +1116,37 @@
       <c r="T2" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="40" t="s">
+      <c r="U2" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V2" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="V2" s="41" t="s">
+    </row>
+    <row r="3" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="29" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="29" t="s">
+      <c r="B3" s="29" t="s">
         <v>35</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>36</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" s="28">
         <v>5336</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I3" s="29" t="s">
         <v>28</v>
@@ -1180,40 +1166,40 @@
         <v>32</v>
       </c>
       <c r="S3" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" s="29"/>
+      <c r="U3" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V3" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="V3" s="41" t="s">
+    </row>
+    <row r="4" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="29" t="s">
+      <c r="B4" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="28">
         <v>4213</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="29" t="s">
         <v>28</v>
@@ -1233,40 +1219,40 @@
         <v>32</v>
       </c>
       <c r="S4" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="42"/>
+      <c r="U4" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V4" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="T4" s="42"/>
-      <c r="U4" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="V4" s="41" t="s">
+    </row>
+    <row r="5" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="29" t="s">
+      <c r="B5" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F5" s="28">
         <v>4213</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I5" s="29" t="s">
         <v>28</v>
@@ -1286,40 +1272,40 @@
         <v>32</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T5" s="42"/>
       <c r="U5" s="60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="V5" s="41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="29" t="s">
+      <c r="B6" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6" s="28">
         <v>4213</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>28</v>
@@ -1339,40 +1325,40 @@
         <v>32</v>
       </c>
       <c r="S6" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T6" s="42"/>
+      <c r="U6" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V6" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="T6" s="42"/>
-      <c r="U6" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="V6" s="41" t="s">
+    </row>
+    <row r="7" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="29" t="s">
+      <c r="B7" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F7" s="28">
         <v>5416</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7" s="29" t="s">
         <v>28</v>
@@ -1392,40 +1378,40 @@
         <v>32</v>
       </c>
       <c r="S7" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T7" s="42"/>
       <c r="U7" s="60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V7" s="41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="29" t="s">
+      <c r="B8" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8" s="28">
         <v>4213</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I8" s="29" t="s">
         <v>28</v>
@@ -1445,40 +1431,40 @@
         <v>32</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T8" s="42"/>
       <c r="U8" s="60" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="V8" s="41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="29" t="s">
+      <c r="B9" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F9" s="28">
         <v>5416</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>28</v>
@@ -1498,40 +1484,40 @@
         <v>32</v>
       </c>
       <c r="S9" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" s="42"/>
+      <c r="U9" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V9" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="T9" s="42"/>
-      <c r="U9" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="V9" s="41" t="s">
+    </row>
+    <row r="10" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="29" t="s">
+      <c r="B10" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" s="28">
         <v>5416</v>
       </c>
       <c r="G10" s="30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>28</v>
@@ -1551,40 +1537,40 @@
         <v>32</v>
       </c>
       <c r="S10" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T10" s="38"/>
+      <c r="U10" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V10" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="T10" s="38"/>
-      <c r="U10" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="V10" s="41" t="s">
+    </row>
+    <row r="11" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="29" t="s">
+      <c r="B11" s="29" t="s">
         <v>43</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>44</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>23</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F11" s="28">
         <v>5416</v>
       </c>
       <c r="G11" s="30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I11" s="29" t="s">
         <v>28</v>
@@ -1604,29 +1590,68 @@
         <v>32</v>
       </c>
       <c r="S11" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T11" s="38"/>
+      <c r="U11" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V11" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="T11" s="38"/>
-      <c r="U11" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="V11" s="41" t="s">
+    </row>
+    <row r="12" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C12" s="31"/>
-      <c r="E12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="39"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
+      <c r="B12" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="28">
+        <v>5416</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="37">
+        <v>0.05</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="38"/>
+      <c r="M12" s="29"/>
+      <c r="Q12" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="T12" s="38"/>
+      <c r="U12" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="V12" s="41" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" spans="1:22" s="10" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="31"/>
@@ -31871,31 +31896,31 @@
   <sheetData>
     <row r="1" spans="1:22" ht="60" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="F1" s="4">
         <v>5870</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J1" s="6">
         <v>1</v>
@@ -31904,7 +31929,7 @@
         <v>29</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M1" s="2">
         <v>3</v>
@@ -31915,49 +31940,49 @@
       <c r="O1" s="2"/>
       <c r="P1" s="7"/>
       <c r="Q1" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S1" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T1" s="8" t="s">
         <v>32</v>
       </c>
       <c r="U1" s="8"/>
       <c r="V1" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="60" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F2" s="4">
         <v>5870</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J2" s="6">
         <v>1</v>
@@ -31966,7 +31991,7 @@
         <v>29</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M2" s="2">
         <v>3</v>
@@ -31976,52 +32001,52 @@
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T2" s="8" t="s">
         <v>32</v>
       </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="60" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" s="4">
         <v>5870</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J3" s="6">
         <v>1</v>
@@ -32030,7 +32055,7 @@
         <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M3" s="2">
         <v>3</v>
@@ -32041,49 +32066,49 @@
       <c r="O3" s="2"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R3" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T3" s="8" t="s">
         <v>32</v>
       </c>
       <c r="U3" s="8"/>
       <c r="V3" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="60" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F4" s="4">
         <v>5870</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J4" s="6">
         <v>1</v>
@@ -32092,7 +32117,7 @@
         <v>29</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M4" s="2">
         <v>3</v>
@@ -32103,20 +32128,20 @@
       <c r="O4" s="2"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="T4" s="8" t="s">
         <v>32</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.15">
